--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS|20260730120000</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -2563,7 +2563,7 @@
     <t>Practitioner.qualification:degree.code.coding:degree</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS|20260223120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS|20260730120000</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.text</t>
@@ -2799,7 +2799,7 @@
     <t>Compétence acquise par le professionnel (competence) R39 ou Compétence exclusive exercée par le professionnel à titre exclusif (competenceExclusive) R40 ou Diplôme d'études spécialisées complémentaires (DESC)DESCnonQualifian R42 ou Capacité (savoir-faire)de médecine (capaciteSavoirFaire) R43 ou Qualification de praticien adjoint contractuel (qualificationPAC) R44 ou Fonction qualifiée (Synonyme: fonctionQualifiee) R45 ou Droit d'exercice complémentaire (Synonyme: droitExerciceComplementaire) R97 ou Orientation particulière (Synonyme: orientationParticuliere) G13 ou Activité ponctuelle du professionnel de type expertise (attributionParticuliere) G13.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS|20251222120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS|20260730120000</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.code.text</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
